--- a/Design/Excel/ET/Datas/Game/Sound.xlsx
+++ b/Design/Excel/ET/Datas/Game/Sound.xlsx
@@ -1191,553 +1191,302 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="8.87272727272727" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="6"/>
-  <cols>
-    <col min="1" max="1" width="8.87272727272727" style="1"/>
-    <col min="2" max="3" width="19.3727272727273" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.1272727272727" style="1" customWidth="1"/>
-    <col min="5" max="5" width="53.8181818181818" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.2545454545455" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.87272727272727" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:7">
-      <c r="B4" s="3">
-        <v>10000</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="B5" s="3">
-        <v>10001</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <ns0:sheetPr/>
+  <ns0:dimension ref="A1:G5"/>
+  <ns0:sheetFormatPr defaultColWidth="8.87272727272727" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="6"/>
+  <ns0:cols>
+    <ns0:col min="1" max="1" width="8.87272727272727" style="1"/>
+    <ns0:col min="2" max="3" width="19.3727272727273" style="1" customWidth="1"/>
+    <ns0:col min="4" max="4" width="17.1272727272727" style="1" customWidth="1"/>
+    <ns0:col min="5" max="5" width="53.8181818181818" style="1" customWidth="1"/>
+    <ns0:col min="6" max="6" width="13" style="1" customWidth="1"/>
+    <ns0:col min="7" max="7" width="12.2545454545455" style="1" customWidth="1"/>
+    <ns0:col min="8" max="16384" width="8.87272727272727" style="1"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1" spans="1:7">
+      <ns0:c r="A1" s="1" t="s">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="B1" s="1" t="s">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="C1" s="1" t="s">
+        <ns0:v>2</ns0:v>
+      </ns0:c>
+      <ns0:c r="D1" s="1" t="s">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+      <ns0:c r="E1" s="1" t="s">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
+      <ns0:c r="F1" s="1" t="s">
+        <ns0:v>5</ns0:v>
+      </ns0:c>
+      <ns0:c r="G1" s="1" t="s">
+        <ns0:v>6</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="2" spans="1:7">
+      <ns0:c r="A2" s="1" t="s">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+      <ns0:c r="B2" s="1" t="s">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+      <ns0:c r="C2" s="1" t="s">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="D2" s="1" t="s">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="E2" s="1" t="s">
+        <ns0:v>10</ns0:v>
+      </ns0:c>
+      <ns0:c r="F2" s="1" t="s">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+      <ns0:c r="G2" s="1" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="3" spans="1:7">
+      <ns0:c r="A3" s="1" t="s">
+        <ns0:v>12</ns0:v>
+      </ns0:c>
+      <ns0:c r="B3" s="1" t="s">
+        <ns0:v>13</ns0:v>
+      </ns0:c>
+      <ns0:c r="C3" s="1" t="s">
+        <ns0:v>14</ns0:v>
+      </ns0:c>
+      <ns0:c r="D3" s="1" t="s">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="E3" s="1" t="s">
+        <ns0:v>16</ns0:v>
+      </ns0:c>
+      <ns0:c r="F3" s="1" t="s">
+        <ns0:v>17</ns0:v>
+      </ns0:c>
+      <ns0:c r="G3" s="1" t="s">
+        <ns0:v>18</ns0:v>
+      </ns0:c>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ns0:pageSetup paperSize="9" orientation="portrait"/>
+  <ns0:headerFooter/>
+</ns0:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="5"/>
-  <cols>
-    <col min="1" max="2" width="11" style="2"/>
-    <col min="3" max="3" width="14.3727272727273" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.8727272727273" style="2" customWidth="1"/>
-    <col min="5" max="5" width="41.7272727272727" style="2" customWidth="1"/>
-    <col min="6" max="6" width="15.2545454545455" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="11" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="B4" s="2">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="B5" s="2">
-        <v>2</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="B6" s="2">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <ns0:sheetPr/>
+  <ns0:dimension ref="A1:F6"/>
+  <ns0:sheetFormatPr defaultColWidth="11" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="5"/>
+  <ns0:cols>
+    <ns0:col min="1" max="2" width="11" style="2"/>
+    <ns0:col min="3" max="3" width="14.3727272727273" style="2" customWidth="1"/>
+    <ns0:col min="4" max="4" width="16.8727272727273" style="2" customWidth="1"/>
+    <ns0:col min="5" max="5" width="41.7272727272727" style="2" customWidth="1"/>
+    <ns0:col min="6" max="6" width="15.2545454545455" style="2" customWidth="1"/>
+    <ns0:col min="7" max="16384" width="11" style="2"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1" spans="1:6">
+      <ns0:c r="A1" s="2" t="s">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="B1" s="2" t="s">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="C1" s="2" t="s">
+        <ns0:v>2</ns0:v>
+      </ns0:c>
+      <ns0:c r="D1" s="2" t="s">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+      <ns0:c r="E1" s="2" t="s">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
+      <ns0:c r="F1" s="2" t="s">
+        <ns0:v>6</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="2" spans="1:6">
+      <ns0:c r="A2" s="2" t="s">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+      <ns0:c r="B2" s="2" t="s">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+      <ns0:c r="C2" s="2" t="s">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="D2" s="2" t="s">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="E2" s="2" t="s">
+        <ns0:v>25</ns0:v>
+      </ns0:c>
+      <ns0:c r="F2" s="2" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="3" spans="1:6">
+      <ns0:c r="A3" s="2" t="s">
+        <ns0:v>12</ns0:v>
+      </ns0:c>
+      <ns0:c r="B3" s="2" t="s">
+        <ns0:v>26</ns0:v>
+      </ns0:c>
+      <ns0:c r="C3" s="2" t="s">
+        <ns0:v>14</ns0:v>
+      </ns0:c>
+      <ns0:c r="D3" s="2" t="s">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="E3" s="2" t="s">
+        <ns0:v>16</ns0:v>
+      </ns0:c>
+      <ns0:c r="F3" s="2" t="s">
+        <ns0:v>18</ns0:v>
+      </ns0:c>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ns0:headerFooter/>
+</ns0:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14" outlineLevelRow="7"/>
-  <cols>
-    <col min="1" max="2" width="11" style="1"/>
-    <col min="3" max="3" width="21.8727272727273" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.1272727272727" style="1" customWidth="1"/>
-    <col min="5" max="5" width="50.2727272727273" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.7545454545455" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.6272727272727" style="1" customWidth="1"/>
-    <col min="8" max="9" width="11" style="1"/>
-    <col min="10" max="10" width="23.7545454545455" style="1" customWidth="1"/>
-    <col min="11" max="11" width="29.3727272727273" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="11" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="B4" s="1">
-        <v>10000</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1</v>
-      </c>
-      <c r="J4" s="1">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="B5" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1</v>
-      </c>
-      <c r="J5" s="1">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="B6" s="1">
-        <v>20000</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1</v>
-      </c>
-      <c r="J6" s="1">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="B7" s="1">
-        <v>20001</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1</v>
-      </c>
-      <c r="J7" s="1">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="B8" s="1">
-        <v>20002</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1</v>
-      </c>
-      <c r="J8" s="1">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
-        <v>100</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <ns0:sheetPr/>
+  <ns0:dimension ref="A1:K8"/>
+  <ns0:sheetFormatPr defaultColWidth="11" defaultRowHeight="14" outlineLevelRow="7"/>
+  <ns0:cols>
+    <ns0:col min="1" max="2" width="11" style="1"/>
+    <ns0:col min="3" max="3" width="21.8727272727273" style="1" customWidth="1"/>
+    <ns0:col min="4" max="4" width="17.1272727272727" style="1" customWidth="1"/>
+    <ns0:col min="5" max="5" width="50.2727272727273" style="1" customWidth="1"/>
+    <ns0:col min="6" max="6" width="22.7545454545455" style="1" customWidth="1"/>
+    <ns0:col min="7" max="7" width="16.6272727272727" style="1" customWidth="1"/>
+    <ns0:col min="8" max="9" width="11" style="1"/>
+    <ns0:col min="10" max="10" width="23.7545454545455" style="1" customWidth="1"/>
+    <ns0:col min="11" max="11" width="29.3727272727273" style="1" customWidth="1"/>
+    <ns0:col min="12" max="16384" width="11" style="1"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1" spans="1:11">
+      <ns0:c r="A1" s="1" t="s">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="B1" s="1" t="s">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="C1" s="1" t="s">
+        <ns0:v>2</ns0:v>
+      </ns0:c>
+      <ns0:c r="D1" s="1" t="s">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+      <ns0:c r="E1" s="1" t="s">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
+      <ns0:c r="F1" s="1" t="s">
+        <ns0:v>36</ns0:v>
+      </ns0:c>
+      <ns0:c r="G1" s="1" t="s">
+        <ns0:v>5</ns0:v>
+      </ns0:c>
+      <ns0:c r="H1" s="1" t="s">
+        <ns0:v>37</ns0:v>
+      </ns0:c>
+      <ns0:c r="I1" s="1" t="s">
+        <ns0:v>6</ns0:v>
+      </ns0:c>
+      <ns0:c r="J1" s="1" t="s">
+        <ns0:v>38</ns0:v>
+      </ns0:c>
+      <ns0:c r="K1" s="1" t="s">
+        <ns0:v>39</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="2" spans="1:11">
+      <ns0:c r="A2" s="1" t="s">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+      <ns0:c r="B2" s="1" t="s">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+      <ns0:c r="C2" s="1" t="s">
+        <ns0:v>40</ns0:v>
+      </ns0:c>
+      <ns0:c r="D2" s="1" t="s">
+        <ns0:v>40</ns0:v>
+      </ns0:c>
+      <ns0:c r="E2" s="1" t="s">
+        <ns0:v>41</ns0:v>
+      </ns0:c>
+      <ns0:c r="F2" s="1" t="s">
+        <ns0:v>42</ns0:v>
+      </ns0:c>
+      <ns0:c r="G2" s="1" t="s">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+      <ns0:c r="H2" s="1" t="s">
+        <ns0:v>43</ns0:v>
+      </ns0:c>
+      <ns0:c r="I2" s="1" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="J2" s="1" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="K2" s="1" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="3" spans="1:11">
+      <ns0:c r="A3" s="1" t="s">
+        <ns0:v>12</ns0:v>
+      </ns0:c>
+      <ns0:c r="B3" s="1" t="s">
+        <ns0:v>13</ns0:v>
+      </ns0:c>
+      <ns0:c r="C3" s="1" t="s">
+        <ns0:v>14</ns0:v>
+      </ns0:c>
+      <ns0:c r="D3" s="1" t="s">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="E3" s="1" t="s">
+        <ns0:v>16</ns0:v>
+      </ns0:c>
+      <ns0:c r="F3" s="1" t="s">
+        <ns0:v>44</ns0:v>
+      </ns0:c>
+      <ns0:c r="G3" s="1" t="s">
+        <ns0:v>17</ns0:v>
+      </ns0:c>
+      <ns0:c r="H3" s="1" t="s">
+        <ns0:v>45</ns0:v>
+      </ns0:c>
+      <ns0:c r="I3" s="1" t="s">
+        <ns0:v>18</ns0:v>
+      </ns0:c>
+      <ns0:c r="J3" s="1" t="s">
+        <ns0:v>46</ns0:v>
+      </ns0:c>
+      <ns0:c r="K3" s="1" t="s">
+        <ns0:v>47</ns0:v>
+      </ns0:c>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ns0:pageSetup paperSize="9" orientation="portrait"/>
+  <ns0:headerFooter/>
+</ns0:worksheet>
 </file>
--- a/Design/Excel/ET/Datas/Game/Sound.xlsx
+++ b/Design/Excel/ET/Datas/Game/Sound.xlsx
@@ -1364,7 +1364,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <ns0:sheetPr/>
-  <ns0:dimension ref="A1:K8"/>
+  <ns0:dimension ref="A1:K9"/>
   <ns0:sheetFormatPr defaultColWidth="11" defaultRowHeight="14" outlineLevelRow="7"/>
   <ns0:cols>
     <ns0:col min="1" max="2" width="11" style="1"/>
@@ -1484,6 +1484,246 @@
         <ns0:v>47</ns0:v>
       </ns0:c>
     </ns0:row>
+    <ns0:row r="4">
+      <ns0:c r="B4" t="n">
+        <ns0:v>1101</ns0:v>
+      </ns0:c>
+      <ns0:c r="C4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>ProductPickup</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>拾取确认</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Product/Pickup</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Sound.Default</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G4" t="n">
+        <ns0:v>20</ns0:v>
+      </ns0:c>
+      <ns0:c r="H4" t="b">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="I4" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="J4" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="K4" t="n">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="5">
+      <ns0:c r="B5" t="n">
+        <ns0:v>1102</ns0:v>
+      </ns0:c>
+      <ns0:c r="C5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>ProductPlace</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>放置入容器和分装</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Product/Place</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Sound.Default</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G5" t="n">
+        <ns0:v>20</ns0:v>
+      </ns0:c>
+      <ns0:c r="H5" t="b">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="I5" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="J5" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="K5" t="n">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="6">
+      <ns0:c r="B6" t="n">
+        <ns0:v>1103</ns0:v>
+      </ns0:c>
+      <ns0:c r="C6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>ProductWorkStart</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>实际开始加工</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Product/WorkStart</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Sound.Default</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G6" t="n">
+        <ns0:v>40</ns0:v>
+      </ns0:c>
+      <ns0:c r="H6" t="b">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="I6" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="J6" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="K6" t="n">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="7">
+      <ns0:c r="B7" t="n">
+        <ns0:v>1104</ns0:v>
+      </ns0:c>
+      <ns0:c r="C7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>ProductWorkFinished</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>实际加工完成</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Product/WorkFinished</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Sound.Default</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G7" t="n">
+        <ns0:v>64</ns0:v>
+      </ns0:c>
+      <ns0:c r="H7" t="b">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="I7" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="J7" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="K7" t="n">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="8">
+      <ns0:c r="B8" t="n">
+        <ns0:v>1105</ns0:v>
+      </ns0:c>
+      <ns0:c r="C8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>ProductServe</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>实际交付成功</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Product/Serve</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Sound.Default</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G8" t="n">
+        <ns0:v>80</ns0:v>
+      </ns0:c>
+      <ns0:c r="H8" t="b">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="I8" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="J8" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="K8" t="n">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="9">
+      <ns0:c r="B9" t="n">
+        <ns0:v>1106</ns0:v>
+      </ns0:c>
+      <ns0:c r="C9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>ProductLevelComplete</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>本关自然完成</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Product/LevelComplete</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Sound.Default</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G9" t="n">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="H9" t="b">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="I9" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="J9" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="K9" t="n">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+    </ns0:row>
   </ns0:sheetData>
   <ns0:pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ns0:pageSetup paperSize="9" orientation="portrait"/>
